--- a/out/S05_clinic_appointment_booking/agent3/agent3_test_cases_with_paths.xlsx
+++ b/out/S05_clinic_appointment_booking/agent3/agent3_test_cases_with_paths.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>12 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
+          <t>10 test(s): TC-FT20, TC-FT21, TC-FT22, TC-FT23, TC-FT24, TC-FT25 ...</t>
         </is>
       </c>
       <c r="Q7" s="8" t="inlineStr">
@@ -1027,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE46"/>
+  <dimension ref="A1:AE44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>3. Dependency / Piping</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr">
@@ -5515,22 +5515,22 @@
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>Q6 quotes the answer given at Q5</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6's wording is built from the answer given at Q5, so the respondent is only asked about what they actually chose.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>A question that quotes the wrong earlier answer reads as a different question entirely to the respondent.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr">
@@ -5546,7 +5546,7 @@
       <c r="N32" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>1. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="AA32" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -5627,7 +5627,7 @@
       </c>
       <c r="AD32" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE32" s="6" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>9. Rule Interaction</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
@@ -5672,22 +5672,22 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>Q6 is shown and reflects its dependency on Q5 at the same time</t>
+          <t>Q6 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 is shown by its display rule and simultaneously reflects its dependency on Q5. Each mechanism can be correct alone and still disagree together.</t>
+          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Individually correct rules can combine into behaviour neither one describes on its own.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr">
@@ -5703,7 +5703,7 @@
       <c r="N33" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes
-then: At Q6, type “xxxxxxxxxx”, then submit.</t>
+then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type “xxxxxxxxxx”, then submit.</t>
+          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -5748,8 +5748,7 @@
       </c>
       <c r="W33" s="6" t="inlineStr">
         <is>
-          <t>1. Q6 is on screen
-2. Q6's wording includes: Yes</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X33" s="6" t="inlineStr">
@@ -5770,7 +5769,7 @@
       </c>
       <c r="AA33" s="6" t="inlineStr">
         <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
+          <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -5785,7 +5784,7 @@
       </c>
       <c r="AD33" s="6" t="inlineStr">
         <is>
-          <t>It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE33" s="6" t="inlineStr">
@@ -5830,22 +5829,22 @@
       </c>
       <c r="H34" s="6" t="inlineStr">
         <is>
-          <t>Q6 rejects an invalid answer</t>
+          <t>Q6 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
+          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr">
@@ -5861,7 +5860,7 @@
       <c r="N34" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes
-then: At Q6, type a 500-character answer, then submit.</t>
+then: At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr">
@@ -5876,17 +5875,17 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>At Q6, type a 500-character answer, then submit.</t>
+          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
         </is>
       </c>
       <c r="S34" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
         </is>
       </c>
       <c r="T34" s="6" t="inlineStr">
@@ -5896,22 +5895,23 @@
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>Q7, Q8</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q6</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y34" s="6" t="inlineStr">
@@ -5930,9 +5930,9 @@
           <t>Derived by rule from the questionnaire's own tables.</t>
         </is>
       </c>
-      <c r="AB34" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB34" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC34" s="8" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AD34" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE34" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -5957,105 +5957,105 @@
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT29</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>1. Flow / Routing</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>Q7 accepts a normal answer and the survey moves on</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+        </is>
+      </c>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>VALID_TYPICAL for every answer</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+        </is>
+      </c>
+      <c r="S35" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
+        </is>
+      </c>
+      <c r="T35" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT29</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G35" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>Q6 rejects an invalid answer</t>
-        </is>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 refuses an answer that breaks its stated rule. The rule is: at least 10 characters; at most 500 characters</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr">
-        <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L35" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M35" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N35" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes
-then: At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T35" s="6" t="inlineStr">
+      <c r="U35" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U35" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
@@ -6063,7 +6063,8 @@
       </c>
       <c r="W35" s="6" t="inlineStr">
         <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
+          <t>1. Q7 is on screen
+2. the next question shown is Q8</t>
         </is>
       </c>
       <c r="X35" s="6" t="inlineStr">
@@ -6078,13 +6079,12 @@
       </c>
       <c r="Z35" s="6" t="inlineStr">
         <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
         </is>
       </c>
       <c r="AA35" s="6" t="inlineStr">
         <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="AD35" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE35" s="6" t="inlineStr">
@@ -6114,155 +6114,154 @@
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>TC-FT30</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>FOCUSED</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>2. Input Validation</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>10. Negative / Robustness</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>Q7 blocks a blank answer</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+        </is>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+        </is>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>FRESH_RESPONDENT</t>
+        </is>
+      </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx
+then: At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>EMPTY</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>At Q7, select nothing at all, then submit.</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+        </is>
+      </c>
+      <c r="S36" s="6" t="inlineStr">
+        <is>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+        </is>
+      </c>
+      <c r="T36" s="6" t="inlineStr">
+        <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT30</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
+          <t>No forward navigation - the same question must reappear.</t>
+        </is>
+      </c>
+      <c r="W36" s="6" t="inlineStr">
+        <is>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q7</t>
+        </is>
+      </c>
+      <c r="X36" s="6" t="inlineStr">
+        <is>
+          <t>Not reached - the respondent cannot progress</t>
+        </is>
+      </c>
+      <c r="Y36" s="6" t="inlineStr">
+        <is>
+          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
+        </is>
+      </c>
+      <c r="Z36" s="6" t="inlineStr">
+        <is>
+          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+        </is>
+      </c>
+      <c r="AA36" s="6" t="inlineStr">
+        <is>
+          <t>QRE explicit - stated directly in the questionnaire.</t>
+        </is>
+      </c>
+      <c r="AB36" s="8" t="inlineStr">
+        <is>
+          <t>RESOLVED</t>
+        </is>
+      </c>
+      <c r="AC36" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AD36" s="6" t="inlineStr">
+        <is>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+        </is>
+      </c>
+      <c r="AE36" s="6" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-      <c r="G36" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>Q6 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q6 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L36" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as Q6.</t>
-        </is>
-      </c>
-      <c r="M36" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes
-then: At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q6 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q6 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>At Q6, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6  (refused at Q6; respondent stays put)</t>
-        </is>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6</t>
-        </is>
-      </c>
-      <c r="T36" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>Q7, Q8</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>No forward navigation - the same question must reappear.</t>
-        </is>
-      </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q6</t>
-        </is>
-      </c>
-      <c r="X36" s="6" t="inlineStr">
-        <is>
-          <t>Not reached - the respondent cannot progress</t>
-        </is>
-      </c>
-      <c r="Y36" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z36" s="6" t="inlineStr">
-        <is>
-          <t>Q6 | Please describe the main problem. | text | — | Show if: Q5 == 'Yes'
-Validate: {"min_length": 10, "max_length": 500}</t>
-        </is>
-      </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>Derived by rule from the questionnaire's own tables.</t>
-        </is>
-      </c>
-      <c r="AB36" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC36" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD36" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE36" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -6272,7 +6271,7 @@
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -6302,12 +6301,12 @@
       </c>
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>Q7 accepts a normal answer and the survey moves on</t>
+          <t>Q8 accepts a normal answer and the survey moves on</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q7 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
@@ -6322,7 +6321,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
@@ -6343,7 +6342,7 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -6378,8 +6377,8 @@
       </c>
       <c r="W37" s="6" t="inlineStr">
         <is>
-          <t>1. Q7 is on screen
-2. the next question shown is Q8</t>
+          <t>1. Q8 is on screen
+2. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
       <c r="X37" s="6" t="inlineStr">
@@ -6394,7 +6393,8 @@
       </c>
       <c r="Z37" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA37" s="6" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q8</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -6459,27 +6459,27 @@
       </c>
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>Q7 blocks a blank answer</t>
+          <t>Q8 accepts a valid answer</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>Prove Q7 refuses to let the respondent past when it is left blank. The questionnaire marks it compulsory, and it is a single question.</t>
+          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q7.</t>
+          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
         </is>
       </c>
       <c r="M38" s="6" t="inlineStr">
@@ -6489,33 +6489,33 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx
-then: At Q7, select nothing at all, then submit.</t>
+          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
+then: At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Every answer before Q7 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q7 is the one the claim turns on.</t>
+          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>At Q7, select nothing at all, then submit.</t>
+          <t>At Q8, type “x”, then submit.</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7  (refused at Q7; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S38" s="6" t="inlineStr">
         <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7</t>
+          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
       <c r="T38" s="6" t="inlineStr">
@@ -6525,23 +6525,22 @@
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>none</t>
         </is>
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q7</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y38" s="6" t="inlineStr">
@@ -6551,7 +6550,8 @@
       </c>
       <c r="Z38" s="6" t="inlineStr">
         <is>
-          <t>Q7 | How likely are you to recommend this service? | single | 0; 1; 2; 3; 4; 5; 6; 7; 8; 9; 10 | Always show</t>
+          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
+Optional</t>
         </is>
       </c>
       <c r="AA38" s="6" t="inlineStr">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="AD38" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE38" s="6" t="inlineStr">
@@ -6601,12 +6601,12 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>1. Flow / Routing</t>
+          <t>2. Input Validation</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10. Negative / Robustness</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a normal answer and the survey moves on</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>Prove that answering Q8 normally moves the respondent on to whatever the questionnaire says comes next, rather than stopping or jumping elsewhere.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Routing is where survey builds most often go wrong. A question that appears for the wrong people, or does not appear for the right ones, corrupts the data without anyone noticing.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -6647,12 +6647,12 @@
       <c r="N39" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: Answer through the whole survey as listed, then observe where it ends.</t>
+then: At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr">
         <is>
-          <t>VALID_TYPICAL for every answer</t>
+          <t>INVALID_BOUNDARY</t>
         </is>
       </c>
       <c r="P39" s="6" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Answer through the whole survey as listed, then observe where it ends.</t>
+          <t>At Q8, type a 501-character answer, then submit.</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -6687,18 +6687,18 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
+          <t>No forward navigation - the same question must reappear.</t>
         </is>
       </c>
       <c r="W39" s="6" t="inlineStr">
         <is>
-          <t>1. Q8 is on screen
-2. the respondent reaches the normal thank-you page</t>
+          <t>1. the survey REFUSES to move on; the same page reappears
+2. an error message is shown against Q8</t>
         </is>
       </c>
       <c r="X39" s="6" t="inlineStr">
         <is>
-          <t>COMPLETE</t>
+          <t>Not reached - the respondent cannot progress</t>
         </is>
       </c>
       <c r="Y39" s="6" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="AD39" s="6" t="inlineStr">
         <is>
-          <t>It does not prove the answer was validated, only that the survey accepted it and moved to the right place. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE39" s="6" t="inlineStr">
@@ -6774,22 +6774,22 @@
       </c>
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>Q8 accepts a valid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 accepts an answer that obeys its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr">
@@ -6805,12 +6805,12 @@
       <c r="N40" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “x”, then submit.</t>
+then: At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr">
         <is>
-          <t>VALID_BOUNDARY</t>
+          <t>EMPTY</t>
         </is>
       </c>
       <c r="P40" s="6" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type “x”, then submit.</t>
+          <t>At Q8, type nothing, then submit.</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="AD40" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE40" s="6" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>10. Negative / Robustness</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -6962,12 +6962,12 @@
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 501-character answer, then submit.</t>
+then: At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr">
         <is>
-          <t>INVALID_BOUNDARY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
@@ -6977,12 +6977,12 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 501-character answer, then submit.</t>
+          <t>At Q8, type a 500-character answer, then submit.</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8  (refused at Q8; respondent stays put)</t>
+          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
       <c r="S41" s="6" t="inlineStr">
@@ -7002,18 +7002,17 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>No forward navigation - the same question must reappear.</t>
+          <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
       <c r="W41" s="6" t="inlineStr">
         <is>
-          <t>1. the survey REFUSES to move on; the same page reappears
-2. an error message is shown against Q8</t>
+          <t>1. the survey ACCEPTS the answer and moves on</t>
         </is>
       </c>
       <c r="X41" s="6" t="inlineStr">
         <is>
-          <t>Not reached - the respondent cannot progress</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="Y41" s="6" t="inlineStr">
@@ -7089,22 +7088,22 @@
       </c>
       <c r="H42" s="6" t="inlineStr">
         <is>
-          <t>Q8 allows a blank answer, being optional</t>
+          <t>Q8 rejects an invalid answer</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
+          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
+          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr">
@@ -7120,12 +7119,12 @@
       <c r="N42" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type nothing, then submit.</t>
+then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr">
         <is>
-          <t>EMPTY</t>
+          <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
       <c r="P42" s="6" t="inlineStr">
@@ -7135,7 +7134,7 @@
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type nothing, then submit.</t>
+          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -7201,7 +7200,7 @@
       </c>
       <c r="AD42" s="6" t="inlineStr">
         <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
+          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
         </is>
       </c>
       <c r="AE42" s="6" t="inlineStr">
@@ -7246,22 +7245,22 @@
       </c>
       <c r="H43" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>Q8 allows a blank answer, being optional</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr">
@@ -7277,7 +7276,7 @@
       <c r="N43" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type a 500-character answer, then submit.</t>
+then: At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr">
@@ -7292,7 +7291,7 @@
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>At Q8, type a 500-character answer, then submit.</t>
+          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -7346,9 +7345,9 @@
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB43" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
+      <c r="AB43" s="10" t="inlineStr">
+        <is>
+          <t>PROVISIONAL</t>
         </is>
       </c>
       <c r="AC43" s="8" t="inlineStr">
@@ -7358,12 +7357,12 @@
       </c>
       <c r="AD43" s="6" t="inlineStr">
         <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
+          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
         </is>
       </c>
       <c r="AE43" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
         </is>
       </c>
     </row>
@@ -7373,57 +7372,57 @@
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>whole survey</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>TC-FT38</t>
+          <t>TC-RT03</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>FOCUSED</t>
+          <t>ROUTE</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>2. Input Validation</t>
+          <t>6. Termination / Disposition</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1. Flow / Routing</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>Q8 rejects an invalid answer</t>
+          <t>End-to-end journey: COMPLETE by way of routing</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>Prove Q8 refuses an answer that breaks its stated rule. The rule is: at most 500 characters</t>
+          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>A rule that is written down but not enforced lets unusable answers into the data. One that is over-enforced blocks valid respondents.</t>
+          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
+          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
         </is>
       </c>
       <c r="M44" s="6" t="inlineStr">
@@ -7432,406 +7431,92 @@
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type “O'Brien said "yes" &lt;50% &amp; more”, then submit.</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S44" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T44" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V44" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W44" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X44" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y44" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z44" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA44" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB44" s="8" t="inlineStr">
-        <is>
-          <t>RESOLVED</t>
-        </is>
-      </c>
-      <c r="AC44" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD44" s="6" t="inlineStr">
-        <is>
-          <t>It proves one direction of one rule at one question. The opposite direction is a separate test. It does not prove anything about questions after the one under test, because the journey stops there.</t>
-        </is>
-      </c>
-      <c r="AE44" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="n">
-        <v>41</v>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="inlineStr">
-        <is>
-          <t>TC-FT39</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>FOCUSED</t>
-        </is>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
-        <is>
-          <t>2. Input Validation</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 allows a blank answer, being optional</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Prove Q8 lets the respondent through with no answer, because the questionnaire marks it optional.</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>A compulsory question that lets people through blank produces missing data that cannot be recovered afterwards.</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L45" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P04 (Completing respondent — Q5=No) as far as Q8.</t>
-        </is>
-      </c>
-      <c r="M45" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N45" s="6" t="inlineStr">
-        <is>
-          <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
-then: At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>VALID_TYPICAL for every answer</t>
-        </is>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>Every answer before Q8 is the first valid option, chosen only to reach the question under test without triggering anything else. The answer at Q8 is the one the claim turns on.</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>At Q8, type 3 spaces and nothing else, then submit.</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
-        </is>
-      </c>
-      <c r="S45" s="6" t="inlineStr">
-        <is>
-          <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
-        </is>
-      </c>
-      <c r="T45" s="6" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="U45" s="6" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="V45" s="6" t="inlineStr">
-        <is>
-          <t>Each listed question is followed immediately by the next in the sequence.</t>
-        </is>
-      </c>
-      <c r="W45" s="6" t="inlineStr">
-        <is>
-          <t>1. the survey ACCEPTS the answer and moves on</t>
-        </is>
-      </c>
-      <c r="X45" s="6" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="Y45" s="6" t="inlineStr">
-        <is>
-          <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
-        </is>
-      </c>
-      <c r="Z45" s="6" t="inlineStr">
-        <is>
-          <t>Q8 | What is the single most important improvement you would suggest? | text | — | Validate: {"max_length": 500}
-Optional</t>
-        </is>
-      </c>
-      <c r="AA45" s="6" t="inlineStr">
-        <is>
-          <t>QRE explicit - stated directly in the questionnaire.</t>
-        </is>
-      </c>
-      <c r="AB45" s="10" t="inlineStr">
-        <is>
-          <t>PROVISIONAL</t>
-        </is>
-      </c>
-      <c r="AC45" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="AD45" s="6" t="inlineStr">
-        <is>
-          <t>It proves only the compulsory setting on this question. Whether the flag is set correctly on other questions is checked separately, question by question.</t>
-        </is>
-      </c>
-      <c r="AE45" s="6" t="inlineStr">
-        <is>
-          <t>Leans on an unconfirmed reading: whitespace_is_an_answer</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>whole survey</t>
-        </is>
-      </c>
-      <c r="C46" s="7" t="inlineStr">
-        <is>
-          <t>TC-RT03</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>ROUTE</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>6. Termination / Disposition</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>1. Flow / Routing</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>End-to-end journey: COMPLETE by way of routing</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>Prove that a respondent answering as listed is shown exactly this sequence of questions, in this order, and ends at COMPLETE by way of the routing, checked at ?. Condition: . They should then see: “Thank you. Your response has been recorded.”</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
-        <is>
-          <t>Screening someone out incorrectly loses a valid respondent and the money spent recruiting them. Failing to screen someone out puts the wrong person in the sample.</t>
-        </is>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>Travel path P03 (Completing respondent — Q5=Yes) as far as the end.</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>FRESH_RESPONDENT</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="inlineStr">
         <is>
           <t>S1 = Yes; S2 = Yes; Q1 = Phone; Q2 = Very poor; Q3 = Very poor; Q4 = Availability; Q5 = Yes; Q6 = xxxxxxxxxx; Q7 = 0
 then: Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="O46" s="6" t="inlineStr">
+      <c r="O44" s="6" t="inlineStr">
         <is>
           <t>VALID_TYPICAL for every answer</t>
         </is>
       </c>
-      <c r="P46" s="6" t="inlineStr">
+      <c r="P44" s="6" t="inlineStr">
         <is>
           <t>Chosen to walk the whole survey without triggering a screen-out.</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>Answer through the whole survey as listed, then observe where it ends.</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>S1 -&gt; S2 -&gt; DT1 -&gt; Q1 -&gt; Q2 -&gt; Q3 -&gt; Q4 -&gt; Q5 -&gt; Q6 -&gt; Q7 -&gt; Q8</t>
         </is>
       </c>
-      <c r="S46" s="6" t="inlineStr">
+      <c r="S44" s="6" t="inlineStr">
         <is>
           <t>S1, S2, DT1, Q1, Q2, Q3, Q4, Q5, Q6, Q7, Q8</t>
         </is>
       </c>
-      <c r="T46" s="6" t="inlineStr">
+      <c r="T44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="U44" s="6" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="V46" s="6" t="inlineStr">
+      <c r="V44" s="6" t="inlineStr">
         <is>
           <t>Each listed question is followed immediately by the next in the sequence.</t>
         </is>
       </c>
-      <c r="W46" s="6" t="inlineStr">
+      <c r="W44" s="6" t="inlineStr">
         <is>
           <t>1. the respondent reaches the normal thank-you page</t>
         </is>
       </c>
-      <c r="X46" s="6" t="inlineStr">
+      <c r="X44" s="6" t="inlineStr">
         <is>
           <t>COMPLETE</t>
         </is>
       </c>
-      <c r="Y46" s="6" t="inlineStr">
+      <c r="Y44" s="6" t="inlineStr">
         <is>
           <t>Page render per question, plus the ordered sequence log and any validation message shown.</t>
         </is>
       </c>
-      <c r="Z46" s="6" t="inlineStr">
+      <c r="Z44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA46" s="6" t="inlineStr">
+      <c r="AA44" s="6" t="inlineStr">
         <is>
           <t>QRE explicit - stated directly in the questionnaire.</t>
         </is>
       </c>
-      <c r="AB46" s="8" t="inlineStr">
+      <c r="AB44" s="8" t="inlineStr">
         <is>
           <t>RESOLVED</t>
         </is>
       </c>
-      <c r="AC46" s="8" t="inlineStr">
+      <c r="AC44" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="AD46" s="6" t="inlineStr">
+      <c r="AD44" s="6" t="inlineStr">
         <is>
           <t>It does not prove any validation rule: every answer on this path is deliberately valid. It does not prove randomization or quota behaviour.</t>
         </is>
       </c>
-      <c r="AE46" s="6" t="inlineStr">
+      <c r="AE44" s="6" t="inlineStr">
         <is>
           <t>-</t>
         </is>
